--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_IMMO SA MARINA CIUTAT D’INCA BASQUET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_IMMO SA MARINA CIUTAT D’INCA BASQUET.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>59.3737</v>
+        <v>36.6791</v>
       </c>
       <c r="E2" t="n">
-        <v>45.3108</v>
+        <v>26.9508</v>
       </c>
       <c r="F2" t="n">
-        <v>14.0629</v>
+        <v>9.728300000000001</v>
       </c>
       <c r="G2" t="n">
         <v>9.295999999999999</v>
@@ -610,13 +610,13 @@
         <v>57.9284</v>
       </c>
       <c r="S2" t="n">
-        <v>47.4207</v>
+        <v>24.7262</v>
       </c>
       <c r="T2" t="n">
-        <v>34.4095</v>
+        <v>16.0495</v>
       </c>
       <c r="U2" t="n">
-        <v>13.0118</v>
+        <v>8.6767</v>
       </c>
       <c r="V2" t="n">
         <v>-5.080100000000001</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>24.7334</v>
+        <v>14.5269</v>
       </c>
       <c r="E3" t="n">
-        <v>21.2116</v>
+        <v>-1.173300000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5219</v>
+        <v>15.7001</v>
       </c>
       <c r="G3" t="n">
-        <v>-18.0493</v>
+        <v>19.2615</v>
       </c>
       <c r="H3" t="n">
-        <v>-15.0588</v>
+        <v>13.3298</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.9909</v>
+        <v>5.931500000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8068</v>
+        <v>43.2231</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.983599999999999</v>
+        <v>22.2008</v>
       </c>
       <c r="L3" t="n">
-        <v>8.7911</v>
+        <v>21.0227</v>
       </c>
       <c r="M3" t="n">
-        <v>-22.8563</v>
+        <v>-23.9623</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.0749</v>
+        <v>-8.870900000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.7816</v>
+        <v>-15.0911</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.7776</v>
+        <v>-8.927100000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-35.5103</v>
+        <v>-63.2846</v>
       </c>
       <c r="R3" t="n">
-        <v>32.7336</v>
+        <v>54.3576</v>
       </c>
       <c r="S3" t="n">
-        <v>45.9133</v>
+        <v>8.5579</v>
       </c>
       <c r="T3" t="n">
-        <v>32.5267</v>
+        <v>4.9284</v>
       </c>
       <c r="U3" t="n">
-        <v>13.3867</v>
+        <v>3.6295</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3529000000000007</v>
+        <v>-4.3651</v>
       </c>
       <c r="W3" t="n">
-        <v>19.3886</v>
+        <v>13.9597</v>
       </c>
       <c r="X3" t="n">
-        <v>-19.7417</v>
+        <v>-18.3247</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. AGUILO RODRIGUEZ</t>
+          <t>M. COLL JANER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>17.425</v>
+        <v>6.0464</v>
       </c>
       <c r="E4" t="n">
-        <v>15.7442</v>
+        <v>0.8812000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6807</v>
+        <v>5.1651</v>
       </c>
       <c r="G4" t="n">
-        <v>-13.4995</v>
+        <v>0.4867000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.0735</v>
+        <v>-1.3362</v>
       </c>
       <c r="I4" t="n">
-        <v>-11.4257</v>
+        <v>1.8228</v>
       </c>
       <c r="J4" t="n">
-        <v>6.7742</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>3.911899999999999</v>
+        <v>-0.418</v>
       </c>
       <c r="L4" t="n">
-        <v>2.8624</v>
+        <v>0.7280000000000002</v>
       </c>
       <c r="M4" t="n">
-        <v>-20.2738</v>
+        <v>0.1767000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.985600000000001</v>
+        <v>-0.9181999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-14.288</v>
+        <v>1.0948</v>
       </c>
       <c r="P4" t="n">
-        <v>17.0611</v>
+        <v>2.1822</v>
       </c>
       <c r="Q4" t="n">
-        <v>-27.1783</v>
+        <v>-2.1822</v>
       </c>
       <c r="R4" t="n">
-        <v>44.24</v>
+        <v>4.3645</v>
       </c>
       <c r="S4" t="n">
-        <v>30.1745</v>
+        <v>2.171</v>
       </c>
       <c r="T4" t="n">
-        <v>26.592</v>
+        <v>1.2812</v>
       </c>
       <c r="U4" t="n">
-        <v>3.5825</v>
+        <v>0.8898</v>
       </c>
       <c r="V4" t="n">
-        <v>-16.3114</v>
+        <v>1.2065</v>
       </c>
       <c r="W4" t="n">
-        <v>9.556100000000001</v>
+        <v>1.4725</v>
       </c>
       <c r="X4" t="n">
-        <v>-25.8674</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. COLL JANER</t>
+          <t>M. AGUILO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2437</v>
+        <v>4.388399999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3030999999999999</v>
+        <v>2.9504</v>
       </c>
       <c r="F5" t="n">
-        <v>4.9405</v>
+        <v>1.4379</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4867000000000001</v>
+        <v>-13.4995</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3362</v>
+        <v>-2.0735</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8228</v>
+        <v>-11.4257</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3100000000000001</v>
+        <v>6.7742</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.418</v>
+        <v>3.911899999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7280000000000002</v>
+        <v>2.8624</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1767000000000001</v>
+        <v>-20.2738</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9181999999999999</v>
+        <v>-5.985600000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0948</v>
+        <v>-14.288</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1822</v>
+        <v>17.0611</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1822</v>
+        <v>-27.1783</v>
       </c>
       <c r="R5" t="n">
-        <v>4.3645</v>
+        <v>44.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3684</v>
+        <v>17.1382</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7031000000000001</v>
+        <v>13.7992</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6654</v>
+        <v>3.3394</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2065</v>
+        <v>-16.3114</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4725</v>
+        <v>9.556100000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>-25.8674</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. RODRIGUEZ DOMINGUEZ</t>
+          <t>J. RIERA MESTRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.343</v>
+        <v>3.880000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2602</v>
+        <v>2.5272</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6032</v>
+        <v>1.353</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2806</v>
+        <v>-2.8486</v>
       </c>
       <c r="H6" t="n">
-        <v>0.121</v>
+        <v>-0.7456999999999998</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4016</v>
+        <v>-2.1027</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3226</v>
+        <v>4.0984</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3226</v>
+        <v>3.2545</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.8440999999999995</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6032</v>
+        <v>-6.9472</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2016</v>
+        <v>-4.0003</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4016</v>
+        <v>-2.947</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>6.149999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-5.3563</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>11.5064</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0623</v>
+        <v>0.5541000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0623</v>
+        <v>-1.5013</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.0556</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.02479999999999977</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>5.2865</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-5.2618</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. RIERA MESTRE</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6105999999999996</v>
+        <v>1.6721</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.270500000000001</v>
+        <v>-1.254599999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6602000000000006</v>
+        <v>2.9276</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.8486</v>
+        <v>-22.8063</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7456999999999998</v>
+        <v>5.4309</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1027</v>
+        <v>-28.2374</v>
       </c>
       <c r="J7" t="n">
-        <v>4.0984</v>
+        <v>6.6501</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2545</v>
+        <v>17.7948</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8440999999999995</v>
+        <v>-11.1449</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.9472</v>
+        <v>-29.4567</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.0003</v>
+        <v>-12.3641</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.947</v>
+        <v>-17.0927</v>
       </c>
       <c r="P7" t="n">
-        <v>6.149999999999999</v>
+        <v>23.6076</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.3563</v>
+        <v>-35.1138</v>
       </c>
       <c r="R7" t="n">
-        <v>11.5064</v>
+        <v>58.7217</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.9365</v>
+        <v>8.920999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-5.2993</v>
+        <v>7.1786</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3628</v>
+        <v>1.7417</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02479999999999977</v>
+        <v>-8.0501</v>
       </c>
       <c r="W7" t="n">
-        <v>5.2865</v>
+        <v>20.03</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.2618</v>
+        <v>-28.0803</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.682100000000002</v>
+        <v>0.9347999999999992</v>
       </c>
       <c r="E8" t="n">
-        <v>-19.1417</v>
+        <v>3.7871</v>
       </c>
       <c r="F8" t="n">
-        <v>12.4598</v>
+        <v>-2.8525</v>
       </c>
       <c r="G8" t="n">
-        <v>-28.4947</v>
+        <v>-18.0493</v>
       </c>
       <c r="H8" t="n">
-        <v>-10.1166</v>
+        <v>-15.0588</v>
       </c>
       <c r="I8" t="n">
-        <v>-18.378</v>
+        <v>-2.9909</v>
       </c>
       <c r="J8" t="n">
-        <v>-14.7562</v>
+        <v>4.8068</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.9488</v>
+        <v>-3.983599999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-10.8072</v>
+        <v>8.7911</v>
       </c>
       <c r="M8" t="n">
-        <v>-13.7385</v>
+        <v>-22.8563</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.1679</v>
+        <v>-11.0749</v>
       </c>
       <c r="O8" t="n">
-        <v>-7.5707</v>
+        <v>-11.7816</v>
       </c>
       <c r="P8" t="n">
-        <v>14.6805</v>
+        <v>-2.7776</v>
       </c>
       <c r="Q8" t="n">
-        <v>-30.1541</v>
+        <v>-35.5103</v>
       </c>
       <c r="R8" t="n">
-        <v>44.8346</v>
+        <v>32.7336</v>
       </c>
       <c r="S8" t="n">
-        <v>14.1447</v>
+        <v>22.1144</v>
       </c>
       <c r="T8" t="n">
-        <v>13.334</v>
+        <v>15.1022</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8107</v>
+        <v>7.0123</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.0126</v>
+        <v>-0.3529000000000007</v>
       </c>
       <c r="W8" t="n">
-        <v>12.435</v>
+        <v>19.3886</v>
       </c>
       <c r="X8" t="n">
-        <v>-19.4475</v>
+        <v>-19.7417</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>R. RODRIGUEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.861</v>
+        <v>-0.343</v>
       </c>
       <c r="E9" t="n">
-        <v>-17.5659</v>
+        <v>0.2602</v>
       </c>
       <c r="F9" t="n">
-        <v>10.7053</v>
+        <v>-0.6032</v>
       </c>
       <c r="G9" t="n">
-        <v>19.2615</v>
+        <v>-0.2806</v>
       </c>
       <c r="H9" t="n">
-        <v>13.3298</v>
+        <v>0.121</v>
       </c>
       <c r="I9" t="n">
-        <v>5.931500000000001</v>
+        <v>-0.4016</v>
       </c>
       <c r="J9" t="n">
-        <v>43.2231</v>
+        <v>0.3226</v>
       </c>
       <c r="K9" t="n">
-        <v>22.2008</v>
+        <v>0.3226</v>
       </c>
       <c r="L9" t="n">
-        <v>21.0227</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-23.9623</v>
+        <v>-0.6032</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.870900000000001</v>
+        <v>-0.2016</v>
       </c>
       <c r="O9" t="n">
-        <v>-15.0911</v>
+        <v>-0.4016</v>
       </c>
       <c r="P9" t="n">
-        <v>-8.927100000000001</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-63.2846</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>54.3576</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-12.8294</v>
+        <v>-0.0623</v>
       </c>
       <c r="T9" t="n">
-        <v>-11.4643</v>
+        <v>-0.0623</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3655</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.3651</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>13.9597</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-18.3247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. MORRO BALERA</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.6582</v>
+        <v>-4.8026</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.6343</v>
+        <v>-5.696299999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0237</v>
+        <v>0.8934999999999993</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.7874</v>
+        <v>-3.5569</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4021</v>
+        <v>-5.3034</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.385400000000001</v>
+        <v>1.7471</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5805</v>
+        <v>21.5157</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6346000000000001</v>
+        <v>7.158099999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9460000000000002</v>
+        <v>14.3577</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.207</v>
+        <v>-25.0724</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7675</v>
+        <v>-12.4618</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.4395</v>
+        <v>-12.6106</v>
       </c>
       <c r="P10" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>-1.785200000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.3644</v>
+        <v>-39.0814</v>
       </c>
       <c r="R10" t="n">
-        <v>4.3645</v>
+        <v>37.2966</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0921</v>
+        <v>5.0451</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2808</v>
+        <v>5.3246</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8111</v>
+        <v>-0.2791000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7786</v>
+        <v>-4.505500000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4085</v>
+        <v>6.545299999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3701</v>
+        <v>-11.0507</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.9689</v>
+        <v>-5.1416</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.109699999999999</v>
+        <v>1.776400000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.8594</v>
+        <v>-6.9182</v>
       </c>
       <c r="G11" t="n">
         <v>-11.3654</v>
@@ -1312,13 +1312,13 @@
         <v>11.3081</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2632</v>
+        <v>3.5641</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.5248</v>
+        <v>1.3612</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2616</v>
+        <v>2.2028</v>
       </c>
       <c r="V11" t="n">
         <v>-4.6806</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>H. MORRO BALERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.5949</v>
+        <v>-8.638500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.4316</v>
+        <v>-6.3874</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1628</v>
+        <v>-2.251</v>
       </c>
       <c r="G12" t="n">
-        <v>-22.8063</v>
+        <v>-5.7874</v>
       </c>
       <c r="H12" t="n">
-        <v>5.4309</v>
+        <v>-1.4021</v>
       </c>
       <c r="I12" t="n">
-        <v>-28.2374</v>
+        <v>-4.385400000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>6.6501</v>
+        <v>-1.5805</v>
       </c>
       <c r="K12" t="n">
-        <v>17.7948</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.1449</v>
+        <v>-0.9460000000000002</v>
       </c>
       <c r="M12" t="n">
-        <v>-29.4567</v>
+        <v>-4.207</v>
       </c>
       <c r="N12" t="n">
-        <v>-12.3641</v>
+        <v>-0.7675</v>
       </c>
       <c r="O12" t="n">
-        <v>-17.0927</v>
+        <v>-3.4395</v>
       </c>
       <c r="P12" t="n">
-        <v>23.6076</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="Q12" t="n">
-        <v>-35.1138</v>
+        <v>-4.3644</v>
       </c>
       <c r="R12" t="n">
-        <v>58.7217</v>
+        <v>4.3645</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.3462</v>
+        <v>-0.07210000000000007</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9982</v>
+        <v>-0.03370000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.3484</v>
+        <v>-0.03839999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-8.0501</v>
+        <v>-2.7786</v>
       </c>
       <c r="W12" t="n">
-        <v>20.03</v>
+        <v>-0.4085</v>
       </c>
       <c r="X12" t="n">
-        <v>-28.0803</v>
+        <v>-2.3701</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.2819</v>
+        <v>-9.558199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>9.568199999999999</v>
+        <v>10.6562</v>
       </c>
       <c r="F13" t="n">
-        <v>-22.8503</v>
+        <v>-20.2145</v>
       </c>
       <c r="G13" t="n">
         <v>-9.2432</v>
@@ -1468,13 +1468,13 @@
         <v>20.8305</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3744</v>
+        <v>1.3496</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0079</v>
+        <v>3.0959</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.3823</v>
+        <v>-1.7467</v>
       </c>
       <c r="V13" t="n">
         <v>-6.6243</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.556</v>
+        <v>-10.2016</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.7938</v>
+        <v>-23.6932</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7621</v>
+        <v>13.4921</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.5569</v>
+        <v>-28.4947</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.3034</v>
+        <v>-10.1166</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7471</v>
+        <v>-18.378</v>
       </c>
       <c r="J14" t="n">
-        <v>21.5157</v>
+        <v>-14.7562</v>
       </c>
       <c r="K14" t="n">
-        <v>7.158099999999999</v>
+        <v>-3.9488</v>
       </c>
       <c r="L14" t="n">
-        <v>14.3577</v>
+        <v>-10.8072</v>
       </c>
       <c r="M14" t="n">
-        <v>-25.0724</v>
+        <v>-13.7385</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.4618</v>
+        <v>-6.1679</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.6106</v>
+        <v>-7.5707</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.785200000000001</v>
+        <v>14.6805</v>
       </c>
       <c r="Q14" t="n">
-        <v>-39.0814</v>
+        <v>-30.1541</v>
       </c>
       <c r="R14" t="n">
-        <v>37.2966</v>
+        <v>44.8346</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.7082</v>
+        <v>10.625</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.7729</v>
+        <v>8.782400000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.9351</v>
+        <v>1.8429</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.505500000000001</v>
+        <v>-7.0126</v>
       </c>
       <c r="W14" t="n">
-        <v>6.545299999999999</v>
+        <v>12.435</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.0507</v>
+        <v>-19.4475</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-28.5686</v>
+        <v>-21.6893</v>
       </c>
       <c r="E15" t="n">
-        <v>-31.4989</v>
+        <v>-24.2383</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9307</v>
+        <v>2.548699999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-21.5472</v>
@@ -1624,13 +1624,13 @@
         <v>30.3528</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6351999999999998</v>
+        <v>7.5147</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.9127</v>
+        <v>2.3483</v>
       </c>
       <c r="U15" t="n">
-        <v>5.548</v>
+        <v>5.1662</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7134000000000005</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-48.4432</v>
+        <v>-33.144</v>
       </c>
       <c r="E16" t="n">
-        <v>-48.3278</v>
+        <v>-36.5664</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.115400000000001</v>
+        <v>3.421899999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-49.2391</v>
@@ -1702,13 +1702,13 @@
         <v>40.4707</v>
       </c>
       <c r="S16" t="n">
-        <v>-8.580400000000001</v>
+        <v>6.7186</v>
       </c>
       <c r="T16" t="n">
-        <v>-6.0969</v>
+        <v>5.6645</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.4835</v>
+        <v>1.0535</v>
       </c>
       <c r="V16" t="n">
         <v>1.2426</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-49.79260000000001</v>
+        <v>-25.39109999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-61.37609999999998</v>
+        <v>-49.22</v>
       </c>
       <c r="F17" t="n">
-        <v>11.5851</v>
+        <v>23.82879999999999</v>
       </c>
       <c r="G17" t="n">
         <v>-157.674</v>
@@ -1756,10 +1756,10 @@
         <v>104.7162</v>
       </c>
       <c r="K17" t="n">
-        <v>96.38380000000004</v>
+        <v>96.38380000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>8.333999999999996</v>
+        <v>8.334000000000003</v>
       </c>
       <c r="M17" t="n">
         <v>-262.3919</v>
@@ -1771,22 +1771,22 @@
         <v>-153.3102</v>
       </c>
       <c r="P17" t="n">
-        <v>71.41879999999998</v>
+        <v>71.4188</v>
       </c>
       <c r="Q17" t="n">
         <v>-381.8871</v>
       </c>
       <c r="R17" t="n">
-        <v>453.31</v>
+        <v>453.3100000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>94.46410000000002</v>
+        <v>118.8655</v>
       </c>
       <c r="T17" t="n">
-        <v>71.161</v>
+        <v>83.31869999999998</v>
       </c>
       <c r="U17" t="n">
-        <v>23.3036</v>
+        <v>35.5462</v>
       </c>
       <c r="V17" t="n">
         <v>-58.00069999999999</v>
